--- a/Peter/Sectoral Analysis (ISIC)/ISIC4/isic4_country_averages.xlsx
+++ b/Peter/Sectoral Analysis (ISIC)/ISIC4/isic4_country_averages.xlsx
@@ -17,7 +17,7 @@
     <t xml:space="preserve">Country or Area</t>
   </si>
   <si>
-    <t xml:space="preserve">Agriculture</t>
+    <t xml:space="preserve">Primary</t>
   </si>
   <si>
     <t xml:space="preserve">Industry</t>
@@ -29,7 +29,7 @@
     <t xml:space="preserve">Transportation</t>
   </si>
   <si>
-    <t xml:space="preserve">Hotel and Resturant</t>
+    <t xml:space="preserve">Hospitality</t>
   </si>
   <si>
     <t xml:space="preserve">Financial</t>
@@ -500,10 +500,10 @@
         <v>0.0258736144297127</v>
       </c>
       <c r="I2" t="n">
+        <v>0.240855890389118</v>
+      </c>
+      <c r="J2" t="n">
         <v>0.205406999116313</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.240855890389118</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -535,10 +535,10 @@
         <v>0.115573257633427</v>
       </c>
       <c r="I3" t="n">
+        <v>-0.0241966175727225</v>
+      </c>
+      <c r="J3" t="n">
         <v>0.142556241606986</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-0.0241966175727225</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -570,10 +570,10 @@
         <v>0.191611496502019</v>
       </c>
       <c r="I4" t="n">
+        <v>-0.20175982256182</v>
+      </c>
+      <c r="J4" t="n">
         <v>0.0279729351778943</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-0.20175982256182</v>
       </c>
       <c r="K4" t="n">
         <v>1.00000000000001</v>
@@ -605,10 +605,10 @@
         <v>0.0746558449381294</v>
       </c>
       <c r="I5" t="n">
+        <v>0.314847515757579</v>
+      </c>
+      <c r="J5" t="n">
         <v>0.262473348255834</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.314847515757579</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -640,10 +640,10 @@
         <v>0.0598335000196375</v>
       </c>
       <c r="I6" t="n">
+        <v>0.228257548553812</v>
+      </c>
+      <c r="J6" t="n">
         <v>0.315729362730632</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.228257548553812</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -675,10 +675,10 @@
         <v>-0.342673010346931</v>
       </c>
       <c r="I7" t="n">
+        <v>-1.1818693830035</v>
+      </c>
+      <c r="J7" t="n">
         <v>0.726895594182629</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-1.1818693830035</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -710,10 +710,10 @@
         <v>0.0675373817500037</v>
       </c>
       <c r="I8" t="n">
+        <v>0.198403366498471</v>
+      </c>
+      <c r="J8" t="n">
         <v>0.122587305781229</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.198403366498471</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -745,10 +745,10 @@
         <v>0.0241484469849437</v>
       </c>
       <c r="I9" t="n">
+        <v>0.202577779256198</v>
+      </c>
+      <c r="J9" t="n">
         <v>0.196592029701858</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.202577779256198</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.00399956319400146</v>
       </c>
       <c r="I10" t="n">
+        <v>-0.0764753133374929</v>
+      </c>
+      <c r="J10" t="n">
         <v>-0.214983849106138</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-0.0764753133374929</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -815,10 +815,10 @@
         <v>0.0541779818685147</v>
       </c>
       <c r="I11" t="n">
+        <v>0.221616635844906</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.129961094558132</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.221616635844906</v>
       </c>
       <c r="K11" t="n">
         <v>0.972497745897035</v>
@@ -850,10 +850,10 @@
         <v>0.0625469699715289</v>
       </c>
       <c r="I12" t="n">
+        <v>0.186618734761744</v>
+      </c>
+      <c r="J12" t="n">
         <v>0.123959977633507</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.186618734761744</v>
       </c>
       <c r="K12" t="n">
         <v>0.969746560424137</v>
@@ -885,10 +885,10 @@
         <v>0.0363762519996874</v>
       </c>
       <c r="I13" t="n">
+        <v>0.33920123346683</v>
+      </c>
+      <c r="J13" t="n">
         <v>0.159029227467216</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.33920123346683</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -920,10 +920,10 @@
         <v>0.0963363117060582</v>
       </c>
       <c r="I14" t="n">
+        <v>0.352117605516507</v>
+      </c>
+      <c r="J14" t="n">
         <v>0.164217374834608</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.352117605516507</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -955,10 +955,10 @@
         <v>0.0676424985216225</v>
       </c>
       <c r="I15" t="n">
+        <v>0.312853421376857</v>
+      </c>
+      <c r="J15" t="n">
         <v>0.0295657933165058</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.312853421376857</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -990,10 +990,10 @@
         <v>0.0515639903169721</v>
       </c>
       <c r="I16" t="n">
+        <v>0.633723168195803</v>
+      </c>
+      <c r="J16" t="n">
         <v>-0.0214033138159005</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.633723168195803</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1025,13 +1025,13 @@
         <v>1.89439483015931</v>
       </c>
       <c r="I17" t="n">
+        <v>16.245738280247</v>
+      </c>
+      <c r="J17" t="n">
         <v>-0.597009089809499</v>
       </c>
-      <c r="J17" t="n">
-        <v>16.245738280247</v>
-      </c>
       <c r="K17" t="n">
-        <v>0.999999999999888</v>
+        <v>0.999999999999889</v>
       </c>
     </row>
     <row r="18">
@@ -1060,10 +1060,10 @@
         <v>0.0918072638577776</v>
       </c>
       <c r="I18" t="n">
+        <v>0.212861719814655</v>
+      </c>
+      <c r="J18" t="n">
         <v>0.247674728634749</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.212861719814655</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -1095,10 +1095,10 @@
         <v>0.139564884240791</v>
       </c>
       <c r="I19" t="n">
+        <v>0.269629195573542</v>
+      </c>
+      <c r="J19" t="n">
         <v>0.100206603382357</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.269629195573542</v>
       </c>
       <c r="K19" t="n">
         <v>1.1438961806623</v>
@@ -1130,10 +1130,10 @@
         <v>0.0261186466820105</v>
       </c>
       <c r="I20" t="n">
+        <v>0.248691159856228</v>
+      </c>
+      <c r="J20" t="n">
         <v>0.151106472825452</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.248691159856228</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -1165,10 +1165,10 @@
         <v>-0.0675618602685413</v>
       </c>
       <c r="I21" t="n">
+        <v>0.672518058859658</v>
+      </c>
+      <c r="J21" t="n">
         <v>0.091007764270836</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.672518058859658</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1200,10 +1200,10 @@
         <v>0.21577773478665</v>
       </c>
       <c r="I22" t="n">
+        <v>0.217190541565249</v>
+      </c>
+      <c r="J22" t="n">
         <v>0.153965704617508</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.217190541565249</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
@@ -1235,10 +1235,10 @@
         <v>0.002368530805001</v>
       </c>
       <c r="I23" t="n">
+        <v>0.0809851861713338</v>
+      </c>
+      <c r="J23" t="n">
         <v>-0.00700189509530159</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.0809851861713338</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
